--- a/tests/formats/mfn_excel/MFN_example.xlsx
+++ b/tests/formats/mfn_excel/MFN_example.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\en986\Documents\Projects\Alltours\generalized_agv_path_finding\tests\formats\mfn_excel\update\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\en986\Documents\Projects\Alltours\generalized_agv_path_finding\tests\formats\mfn_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FF447C-6791-425B-A25A-CFA562EBC92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852381D4-135C-4AF6-B76A-E90E0C0D8691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="228" windowWidth="30936" windowHeight="16776" xr2:uid="{B8DE84FF-B3E8-4D87-8A95-BDBF8C6662ED}"/>
+    <workbookView xWindow="30612" yWindow="228" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{B8DE84FF-B3E8-4D87-8A95-BDBF8C6662ED}"/>
   </bookViews>
   <sheets>
     <sheet name="NetworkNodes" sheetId="3" r:id="rId1"/>
@@ -19,9 +19,9 @@
     <sheet name="Fleets" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">NetworkConnections!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NetworkNodes!$A$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">NetworkPaths!$D$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">NetworkConnections!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NetworkNodes!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">NetworkPaths!$D$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,14 +44,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="22">
   <si>
     <t>Connection1</t>
   </si>
   <si>
-    <t>[String]</t>
-  </si>
-  <si>
     <t>cal_trans_duration_seconds</t>
   </si>
   <si>
@@ -88,73 +85,9 @@
     <t>x_meter</t>
   </si>
   <si>
-    <t>Die angenommene Wegzeit für den Ebenenwechsel in Sekunden</t>
-  </si>
-  <si>
-    <t>[int]</t>
-  </si>
-  <si>
     <t>Roboter</t>
   </si>
   <si>
-    <t>[double]</t>
-  </si>
-  <si>
-    <t>Id der Node</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Id der </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>unidirektionalen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Connection</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Id des </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>unidirektionalen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Paths</t>
-    </r>
-  </si>
-  <si>
     <t>Path_1A</t>
   </si>
   <si>
@@ -174,13 +107,16 @@
   </si>
   <si>
     <t>fleet</t>
+  </si>
+  <si>
+    <t>Besucher</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,32 +133,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -249,27 +171,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -584,57 +498,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD73832A-1FBC-4985-A5DF-25369F7E8B7C}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>1.5</v>
+      </c>
+      <c r="C2">
+        <v>1.6</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C3">
+        <v>2.4</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -642,43 +562,15 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>2.2999999999999998</v>
+        <v>1.5</v>
       </c>
       <c r="C5">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2.4</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>1.5</v>
-      </c>
-      <c r="C7">
-        <v>1.6</v>
-      </c>
-      <c r="D7">
         <v>0</v>
       </c>
     </row>
@@ -691,7 +583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E622508-6A6C-469D-9F74-98CF2B9013FF}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -700,93 +592,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6"/>
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -798,7 +670,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BDF8D4-F853-400B-A69F-22F8FF9ECE1F}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -809,80 +681,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2"/>
+      <c r="D2">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
         <v>90</v>
       </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5">
-        <v>90</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
+      <c r="E3" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -894,7 +740,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB8B8A65-F99D-4F49-974E-B1A88D75D5CE}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.109375" customWidth="1"/>
@@ -902,19 +748,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>26</v>
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/tests/formats/mfn_excel/MFN_example.xlsx
+++ b/tests/formats/mfn_excel/MFN_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\en986\Documents\Projects\Alltours\generalized_agv_path_finding\tests\formats\mfn_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852381D4-135C-4AF6-B76A-E90E0C0D8691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83D4E26-2946-4B58-955F-71C16BA193B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="228" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{B8DE84FF-B3E8-4D87-8A95-BDBF8C6662ED}"/>
+    <workbookView xWindow="30612" yWindow="228" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{B8DE84FF-B3E8-4D87-8A95-BDBF8C6662ED}"/>
   </bookViews>
   <sheets>
     <sheet name="NetworkNodes" sheetId="3" r:id="rId1"/>
@@ -171,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -184,6 +184,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -707,7 +708,7 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="6">
         <v>90</v>
       </c>
       <c r="E2" t="s">

--- a/tests/formats/mfn_excel/MFN_example.xlsx
+++ b/tests/formats/mfn_excel/MFN_example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\en986\Documents\Projects\Alltours\generalized_agv_path_finding\tests\formats\mfn_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83D4E26-2946-4B58-955F-71C16BA193B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29A7669-74C4-44B5-AFE9-6BBBF8D28503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="228" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{B8DE84FF-B3E8-4D87-8A95-BDBF8C6662ED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{B8DE84FF-B3E8-4D87-8A95-BDBF8C6662ED}"/>
   </bookViews>
   <sheets>
     <sheet name="NetworkNodes" sheetId="3" r:id="rId1"/>
@@ -19,94 +19,101 @@
     <sheet name="Fleets" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">NetworkConnections!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NetworkNodes!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">NetworkPaths!$D$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">NetworkConnections!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NetworkNodes!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">NetworkPaths!$E$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="28">
+  <si>
+    <t>cal_trans_duration_seconds</t>
+  </si>
+  <si>
+    <t>fleets</t>
+  </si>
+  <si>
+    <t>destination_node_name</t>
+  </si>
+  <si>
+    <t>origin_node_name</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>1-E1</t>
+  </si>
+  <si>
+    <t>3-E0</t>
+  </si>
+  <si>
+    <t>2-E0</t>
+  </si>
+  <si>
+    <t>1-E0</t>
+  </si>
+  <si>
+    <t>z_meter</t>
+  </si>
+  <si>
+    <t>y_meter</t>
+  </si>
+  <si>
+    <t>x_meter</t>
+  </si>
+  <si>
+    <t>Roboter</t>
+  </si>
+  <si>
+    <t>Path_1A</t>
+  </si>
+  <si>
+    <t>Path_1B</t>
+  </si>
+  <si>
+    <t>Path_2A</t>
+  </si>
+  <si>
+    <t>Path_2B</t>
+  </si>
+  <si>
+    <t>Roboter | Besucher</t>
+  </si>
+  <si>
+    <t>avg_speed_mps</t>
+  </si>
+  <si>
+    <t>fleet</t>
+  </si>
+  <si>
+    <t>network</t>
+  </si>
+  <si>
+    <t>Network1</t>
+  </si>
+  <si>
+    <t>Network2</t>
+  </si>
+  <si>
+    <t>origin_network</t>
+  </si>
+  <si>
+    <t>destination_network</t>
+  </si>
   <si>
     <t>Connection1</t>
   </si>
   <si>
-    <t>cal_trans_duration_seconds</t>
-  </si>
-  <si>
-    <t>fleets</t>
-  </si>
-  <si>
-    <t>destination_node_name</t>
-  </si>
-  <si>
-    <t>origin_node_name</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>1-E1</t>
-  </si>
-  <si>
-    <t>3-E0</t>
-  </si>
-  <si>
-    <t>2-E0</t>
-  </si>
-  <si>
-    <t>1-E0</t>
-  </si>
-  <si>
-    <t>z_meter</t>
-  </si>
-  <si>
-    <t>y_meter</t>
-  </si>
-  <si>
-    <t>x_meter</t>
-  </si>
-  <si>
-    <t>Roboter</t>
-  </si>
-  <si>
-    <t>Path_1A</t>
-  </si>
-  <si>
-    <t>Path_1B</t>
-  </si>
-  <si>
-    <t>Path_2A</t>
-  </si>
-  <si>
-    <t>Path_2B</t>
-  </si>
-  <si>
-    <t>Roboter | Besucher</t>
-  </si>
-  <si>
-    <t>avg_speed_mps</t>
-  </si>
-  <si>
-    <t>fleet</t>
+    <t>Connection2</t>
   </si>
   <si>
     <t>Besucher</t>
@@ -116,7 +123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,6 +144,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -499,18 +512,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD73832A-1FBC-4985-A5DF-25369F7E8B7C}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>11</v>
@@ -518,65 +531,80 @@
       <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2">
         <v>1.5</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1.6</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>2.4</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2.4</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5">
         <v>1.5</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>1.6</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D3" xr:uid="{722C5049-67F5-4D34-BA8B-C96877DC8B4A}"/>
+  <autoFilter ref="A1:E1" xr:uid="{722C5049-67F5-4D34-BA8B-C96877DC8B4A}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -584,86 +612,103 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E622508-6A6C-469D-9F74-98CF2B9013FF}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D3" xr:uid="{F3B9DDB8-FB25-49C8-981E-1A013ECC792F}"/>
+  <autoFilter ref="E1" xr:uid="{F3B9DDB8-FB25-49C8-981E-1A013ECC792F}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -671,69 +716,89 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BDF8D4-F853-400B-A69F-22F8FF9ECE1F}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.44140625" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="6">
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="6">
         <v>90</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>0</v>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="6">
         <v>90</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
+      <c r="G3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E4" xr:uid="{4A1CA232-A6F5-407D-9A1D-FC8408101890}"/>
+  <autoFilter ref="A1:G4" xr:uid="{4A1CA232-A6F5-407D-9A1D-FC8408101890}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -750,15 +815,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>0.5</v>
@@ -766,7 +831,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>0.4</v>
